--- a/Vendas_empresas.xlsx
+++ b/Vendas_empresas.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_92485C45C1F39E42E268565A893E8C18510380CC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{452E1A0F-1197-474F-B28F-C6C66466DC5B}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e4f8f5140d98e587/Documentos/GitHub/aula13/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_92485C45C1F39E42E268565A893E8C18510380CC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FB51E18-D94E-4CA9-951C-B5C1D4B15BE6}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -163,7 +168,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -212,10 +217,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -253,7 +262,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -359,7 +368,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -501,7 +510,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -510,12 +519,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" customWidth="1"/>
+    <col min="3" max="3" width="14.6328125" customWidth="1"/>
+    <col min="7" max="7" width="13.81640625" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="15.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -547,7 +561,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>101</v>
       </c>
@@ -579,7 +593,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>102</v>
       </c>
@@ -611,7 +625,7 @@
         <v>44111</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>103</v>
       </c>
@@ -643,7 +657,7 @@
         <v>42036</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>104</v>
       </c>
@@ -675,7 +689,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>105</v>
       </c>
@@ -707,7 +721,7 @@
         <v>43590</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>106</v>
       </c>
@@ -739,7 +753,7 @@
         <v>45268</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>107</v>
       </c>
@@ -771,7 +785,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>108</v>
       </c>
@@ -803,7 +817,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>109</v>
       </c>
@@ -835,7 +849,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>110</v>
       </c>
@@ -867,7 +881,7 @@
         <v>45047</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>111</v>
       </c>
@@ -899,7 +913,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>112</v>
       </c>
@@ -931,7 +945,7 @@
         <v>41922</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>113</v>
       </c>
@@ -963,7 +977,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>114</v>
       </c>
@@ -995,7 +1009,7 @@
         <v>44775</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>115</v>
       </c>
@@ -1033,6 +1047,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CD51460BBB3BD64989C0AF0085EB7E4E" ma:contentTypeVersion="42" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="41e95247f3d26be0199051f7ec3e26f0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="86243fb6-e625-4153-bf24-3dbb8808cb3e" xmlns:ns3="29c85e31-c0e5-4fba-ab60-4fce8ca17cbc" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a464040ef587764195de75a71551f205" ns2:_="" ns3:_="">
     <xsd:import namespace="86243fb6-e625-4153-bf24-3dbb8808cb3e"/>
@@ -1490,15 +1513,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1546,13 +1560,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD7DCC7B-18D8-4A97-99DD-AC91EE683D65}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E2D1FE7-FC7F-4AEC-8ACA-D3063C49AB93}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E2D1FE7-FC7F-4AEC-8ACA-D3063C49AB93}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD7DCC7B-18D8-4A97-99DD-AC91EE683D65}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="86243fb6-e625-4153-bf24-3dbb8808cb3e"/>
+    <ds:schemaRef ds:uri="29c85e31-c0e5-4fba-ab60-4fce8ca17cbc"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB441A8B-9B86-4C6B-AB19-AC062BBD11B9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB441A8B-9B86-4C6B-AB19-AC062BBD11B9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="86243fb6-e625-4153-bf24-3dbb8808cb3e"/>
+    <ds:schemaRef ds:uri="29c85e31-c0e5-4fba-ab60-4fce8ca17cbc"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>